--- a/Návrhy_databáze/Návrh_Databáze_Levels.xlsx
+++ b/Návrhy_databáze/Návrh_Databáze_Levels.xlsx
@@ -16,20 +16,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t xml:space="preserve">Uživatel a role</t>
   </si>
   <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Oprávnění</t>
+  </si>
+  <si>
+    <t>Heslo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potvrzení hesla</t>
+  </si>
+  <si>
     <t>Client</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Oprávnění</t>
-  </si>
-  <si>
     <t>IČO</t>
   </si>
   <si>
@@ -73,12 +82,6 @@
   </si>
   <si>
     <t xml:space="preserve">Adresa provozovny</t>
-  </si>
-  <si>
-    <t>Heslo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potvrzení hesla</t>
   </si>
   <si>
     <t>Konfigurace</t>
@@ -413,10 +416,9 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
@@ -424,18 +426,12 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="0" fillId="13" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1078,227 +1074,249 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="3"/>
+      <c r="AL3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="AO3" s="2"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5" t="s">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5" t="s">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5" t="s">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5" t="s">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="3" t="s">
+      <c r="R5" s="4"/>
+      <c r="S5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="s">
+      <c r="T5" s="4"/>
+      <c r="U5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="2" t="s">
+      <c r="V5" s="4"/>
+      <c r="W5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3" t="s">
+      <c r="X5" s="4"/>
+      <c r="Y5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3" t="s">
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3" t="s">
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3" t="s">
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3" t="s">
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AO3" s="3"/>
-      <c r="AQ3" s="1" t="s">
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AR3" s="1"/>
-      <c r="AS3" s="1"/>
-      <c r="AT3" s="1"/>
-      <c r="AU3" s="1"/>
-      <c r="AV3" s="6" t="s">
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="2"/>
+      <c r="AQ5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="6"/>
-      <c r="AY3" s="6" t="s">
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="3" t="s">
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
+      <c r="AZ5" s="6"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="s">
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3" t="s">
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR7" s="5"/>
+      <c r="AS7" s="5"/>
+      <c r="AT7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU7" s="5"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3" t="s">
+      <c r="L9" s="4"/>
+      <c r="M9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="7"/>
-      <c r="AQ5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AR5" s="6"/>
-      <c r="AS5" s="6"/>
-      <c r="AT5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU5" s="6"/>
-      <c r="AZ5" s="7"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="5"/>
+      <c r="N9" s="4"/>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="9" t="s">
-        <v>28</v>
+      <c r="A11" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1434,120 +1452,120 @@
       <c r="EC11" s="1"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="10" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="12" t="s">
+      <c r="H13" s="4"/>
+      <c r="I13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4" t="s">
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="11" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="13" t="s">
+      <c r="H17" s="4"/>
+      <c r="I17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4" t="s">
+      <c r="J17" s="7"/>
+      <c r="K17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="11" t="s">
+      <c r="F19" s="3"/>
+      <c r="G19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="13" t="s">
+      <c r="H19" s="4"/>
+      <c r="I19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="9" t="s">
-        <v>36</v>
+      <c r="A21" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1683,229 +1701,229 @@
       <c r="EC21" s="1"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4" t="s">
+      <c r="A23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="11" t="s">
+      <c r="F23" s="3"/>
+      <c r="G23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="13" t="s">
+      <c r="H23" s="4"/>
+      <c r="I23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="7"/>
+      <c r="K25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4" t="s">
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="11" t="s">
+      <c r="F27" s="3"/>
+      <c r="G27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="13" t="s">
+      <c r="H27" s="4"/>
+      <c r="I27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4" t="s">
+      <c r="J27" s="7"/>
+      <c r="K27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="11" t="s">
+      <c r="F29" s="3"/>
+      <c r="G29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="11"/>
-      <c r="K27" s="13" t="s">
+      <c r="H29" s="4"/>
+      <c r="I29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4" t="s">
+      <c r="J29" s="7"/>
+      <c r="K29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="11" t="s">
+      <c r="F31" s="3"/>
+      <c r="G31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="13" t="s">
+      <c r="H31" s="4"/>
+      <c r="I31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="11" t="s">
+      <c r="G33" s="3"/>
+      <c r="H33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="11"/>
-      <c r="K31" s="13" t="s">
+      <c r="I33" s="4"/>
+      <c r="J33" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="M33" s="14"/>
-      <c r="N33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M33" s="9"/>
+      <c r="N33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2041,87 +2059,87 @@
       <c r="EC35" s="1"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4" t="s">
+      <c r="A37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
+      <c r="D37" s="3"/>
+      <c r="E37" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="5" t="s">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="11" t="s">
+      <c r="H37" s="3"/>
+      <c r="I37" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11" t="s">
+      <c r="J37" s="4"/>
+      <c r="K37" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="11"/>
-      <c r="O37" s="14" t="s">
+      <c r="L37" s="7"/>
+      <c r="M37" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="15" t="s">
+      <c r="N37" s="7"/>
+      <c r="O37" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="R37" s="15"/>
-      <c r="S37" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="16" t="s">
+      <c r="P37" s="9"/>
+      <c r="Q37" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="17" t="s">
+      <c r="R37" s="10"/>
+      <c r="S37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T37" s="8"/>
+      <c r="U37" s="8"/>
+      <c r="V37" s="8"/>
+      <c r="W37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="6"/>
-      <c r="AB37" s="6"/>
-      <c r="AC37" s="18" t="s">
+      <c r="X37" s="11"/>
+      <c r="Y37" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="18"/>
-      <c r="AG37" s="15" t="s">
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="AH37" s="15"/>
-      <c r="AI37" s="19" t="s">
+      <c r="AD37" s="12"/>
+      <c r="AE37" s="12"/>
+      <c r="AF37" s="12"/>
+      <c r="AG37" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="AJ37" s="16"/>
-      <c r="AK37" s="6" t="s">
+      <c r="AH37" s="10"/>
+      <c r="AI37" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AL37" s="6"/>
-      <c r="AM37" s="18" t="s">
+      <c r="AJ37" s="11"/>
+      <c r="AK37" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AN37" s="18"/>
-      <c r="AO37" s="18"/>
-      <c r="AP37" s="18"/>
-      <c r="AQ37" s="18"/>
+      <c r="AL37" s="5"/>
+      <c r="AM37" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN37" s="12"/>
+      <c r="AO37" s="12"/>
+      <c r="AP37" s="12"/>
+      <c r="AQ37" s="12"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="9" t="s">
-        <v>57</v>
+      <c r="A39" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2257,150 +2275,150 @@
       <c r="EC39" s="1"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5" t="s">
+      <c r="A41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="11" t="s">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="13" t="s">
+      <c r="G41" s="4"/>
+      <c r="H41" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="K41" s="13"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K41" s="8"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5" t="s">
+      <c r="A43" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="11" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I43" s="11"/>
-      <c r="J43" s="13" t="s">
+      <c r="G43" s="4"/>
+      <c r="H43" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K43" s="13"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" s="8"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="5" t="s">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="11" t="s">
+      <c r="E45" s="3"/>
+      <c r="F45" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J45" s="11"/>
-      <c r="K45" s="13" t="s">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L45" s="13"/>
-      <c r="M45" s="14" t="s">
+      <c r="J45" s="7"/>
+      <c r="K45" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="N45" s="14"/>
-      <c r="O45" s="15" t="s">
+      <c r="L45" s="8"/>
+      <c r="M45" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="21" t="s">
+      <c r="N45" s="9"/>
+      <c r="O45" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R45" s="21"/>
-      <c r="S45" s="21"/>
-      <c r="T45" s="21"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="R45" s="14"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="11" t="s">
+      <c r="A47" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I47" s="11"/>
-      <c r="J47" s="13" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K47" s="13"/>
-      <c r="L47" s="14" t="s">
+      <c r="I47" s="7"/>
+      <c r="J47" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="M47" s="14"/>
-      <c r="N47" s="15" t="s">
+      <c r="K47" s="8"/>
+      <c r="L47" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="O47" s="15"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O47" s="10"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I49" s="11"/>
-      <c r="J49" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K49" s="13"/>
-      <c r="L49" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M49" s="14"/>
+      <c r="M49" s="9"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="9" t="s">
-        <v>82</v>
+      <c r="A51" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2536,101 +2554,101 @@
       <c r="EC51" s="1"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="5" t="s">
+      <c r="A53" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="11" t="s">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I53" s="11"/>
-      <c r="J53" s="13" t="s">
+      <c r="G53" s="4"/>
+      <c r="H53" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K53" s="13"/>
-      <c r="L53" s="14" t="s">
+      <c r="I53" s="7"/>
+      <c r="J53" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="M53" s="14"/>
-      <c r="N53" s="15" t="s">
+      <c r="K53" s="8"/>
+      <c r="L53" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="O53" s="15"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O53" s="10"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I55" s="7"/>
+      <c r="J55" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K55" s="8"/>
+      <c r="L55" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55" s="9"/>
+      <c r="N55" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="11" t="s">
+      <c r="O55" s="10"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I55" s="11"/>
-      <c r="J55" s="13" t="s">
+      <c r="G57" s="4"/>
+      <c r="H57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K55" s="13"/>
-      <c r="L55" s="14" t="s">
+      <c r="I57" s="7"/>
+      <c r="J57" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="M55" s="14"/>
-      <c r="N55" s="15" t="s">
+      <c r="K57" s="8"/>
+      <c r="L57" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="O55" s="15"/>
-    </row>
-    <row r="57" ht="14.25">
-      <c r="A57" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I57" s="11"/>
-      <c r="J57" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="K57" s="13"/>
-      <c r="L57" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="M57" s="14"/>
-      <c r="N57" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="O57" s="15"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O57" s="10"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="9" t="s">
-        <v>92</v>
+      <c r="A59" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2766,26 +2784,26 @@
       <c r="EC59" s="1"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5" t="s">
+      <c r="A61" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H61" s="11"/>
-      <c r="I61" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="J61" s="13"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J61" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
